--- a/data/seed/portfolio/L-2024-9037/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-9037/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I173"/>
+  <dimension ref="A1:I193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,40 +558,40 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>12488000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>7374000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №21/26</t>
+          <t>Оплата за товар по счет-фактуре №3559 от 01.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>8862000</v>
+        <v>1111000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SHARTNOMA №5/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Shartnoma №142/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,38 +642,38 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>1806000</v>
+        <v>692000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3197 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2171 от 01.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,38 +683,38 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>77110000</v>
+        <v>3292000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8900 за поставленный товар</t>
+          <t>Предоплата за товар по договору №225/26 от 02.07.2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -724,38 +724,38 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>5275000</v>
+        <v>1035000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №15126 от 06.07.2026</t>
+          <t>Предоплата за товар по дог. №179/26 от 02.07.2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -764,39 +764,39 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3085000</v>
+        <v>3604000</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Farg'ona Qurilish AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №89/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №8851</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -804,35 +804,40 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>13078000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>5247000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Andijon Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №8505</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №7599 ОТ 03.07.2026, В Т.Ч. ДС 12%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -840,40 +845,40 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>16458000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>2543000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №261/26</t>
+          <t>Оплата по с/ф №1998 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -883,38 +888,38 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>9236000</v>
+        <v>784000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №229/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3450 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -924,38 +929,38 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>5264000</v>
+        <v>6419000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Qarshi Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>397457622</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000801727020001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1025 за поставленный товар</t>
+          <t>Оплата по с/ф №2832 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -963,40 +968,40 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>1507000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>3393000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>344740732</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000981258976001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по дог. №29/22</t>
+          <t>Оплата по счет-фактуре №2738 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1006,38 +1011,38 @@
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>26347000</v>
+        <v>1677000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №156/26 от 10.07.2026</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3161 06.07.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1047,38 +1052,38 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>10043000</v>
+        <v>783000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Tong Metall Servis AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>346612847</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000528839589001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №197/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3783 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1087,39 +1092,39 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9350000</v>
+        <v>1526000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guliston Tekstil MChJ</t>
+          <t>Farg'ona Qurilish AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>392648014</t>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000213542681001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №168/26</t>
+          <t>Предоплата за материалы по договору №153/26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,40 +1132,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>1510000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>8169000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lazzat Meva Eksport MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>271470811</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000907491689001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №29/26 от 13.07.2026</t>
+          <t>Оплата за транспортные услуги по дог. №218/26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1169,39 +1174,34 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>21322000</v>
+        <v>13078000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Durdona Farm Savdo XK</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>318867866</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000278876047001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4213</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1209,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>1783000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>34945000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>364282370</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000447549855001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Предоплата за товар по договору №48/26 от 07.07.2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,40 +1250,40 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>1783000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>1218000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №120/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1291,40 +1291,40 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>3123000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>1507000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Xiva Qurilish MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>372008215</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000784862057001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №146/26, QQS 12%</t>
+          <t>Арендная плата за июль 2026 г. по дог. №48/22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1332,40 +1332,40 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>2933000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>4477000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4763 ОТ 16.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8713</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1373,40 +1373,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>13496000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>766000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guliston Tekstil MChJ</t>
+          <t>Angren Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>392648014</t>
+          <t>364282370</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000213542681001</t>
+          <t>20208000447549855001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5976</t>
+          <t>Shartnoma №264/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1416,38 +1416,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>4532000</v>
+        <v>32493000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5806 за поставленный товар</t>
+          <t>Оплата по с/ф №5484 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,40 +1455,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>3578000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>729000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guliston Tekstil MChJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>392648014</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000213542681001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №119/26</t>
+          <t>Оплата по счет-фактуре №3811 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1497,39 +1497,39 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>7443000</v>
+        <v>41215000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Sharq Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>230815755</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000109215286001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №60/26 от 17.07.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №7351</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1537,40 +1537,40 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>2804000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>20541000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Farg'ona Qurilish AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1487 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №1038</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1580,38 +1580,38 @@
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>2678000</v>
+        <v>19252000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4063 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №72/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1621,21 +1621,21 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>1609000</v>
+        <v>14176000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1645,14 +1645,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5124 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №192/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1660,40 +1660,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>3112000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>2347000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №287/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3430</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,40 +1701,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>5159000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>754000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guliston Tekstil MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>392648014</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000213542681001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №273/26</t>
+          <t>Оплата за продукцию по договору №101/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1743,34 +1743,39 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>12100000</v>
+        <v>1783000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9037)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16307000271935222417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9037 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1779,39 +1784,39 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>19367000</v>
+        <v>1783000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ №6415</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1824,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>3543000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>11119000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2184</t>
+          <t>Предоплата за товар по дог. №253/26 от 15.07.2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1865,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>1483000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>18065000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Farg'ona Qurilish AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №95/26, НДС 12%</t>
+          <t>Предоплата за материалы по дог. №292/26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1901,40 +1906,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>2558000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>793000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Mahsulot uchun to'lov, shartnoma №18/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1944,38 +1949,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>6050000</v>
+        <v>2984000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Angren Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>364282370</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000447549855001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №27/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6993 20.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,21 +1990,21 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>1646000</v>
+        <v>2316000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2009,14 +2014,14 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дговору №150/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №30/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2029,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>32666000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>1169000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>309130513</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000231828708001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №171/26</t>
+          <t>Оплата по счет-фактуре №4330 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2067,21 +2072,21 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>13276000</v>
+        <v>690000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2091,14 +2096,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7684 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №273/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2111,35 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>7930000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>12100000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>245987287</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9037)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>16307000271935222417</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4737</t>
+          <t>Kredit shartnomasi L-2024-9037 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2149,38 +2149,38 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>3495000</v>
+        <v>7578000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1735 27.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №109/26 от 21.07.2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2190,38 +2190,38 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>3258000</v>
+        <v>1750000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №48/26 от 27.07.2026</t>
+          <t>Оплата за продукцию по договору №226/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,40 +2229,40 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>2512000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>2513000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7535 за поставленный товар</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,40 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>942000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>5645000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000336102030001</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Оплата за товар по счет-фактуре №355 от 22.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>4812000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>1990000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durdona Farm Savdo XK</t>
+          <t>Angren Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>318867866</t>
+          <t>364282370</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000278876047001</t>
+          <t>20208000447549855001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №139/26</t>
+          <t>Оплата за продукцию по дог. №136/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2352,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>5207000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>10681000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9169</t>
+          <t>Оплата по счет-фактуре №2791 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2393,40 +2393,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>7409000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>1323000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>309130513</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000231828708001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №289/26 от 28.07.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №623 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2436,21 +2436,21 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>4169000</v>
+        <v>774000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,14 +2460,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shartnoma №260/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №246/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2476,39 +2476,39 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>3369000</v>
+        <v>942000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000185907515001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1695</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,23 +2516,23 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>3392000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>3442000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №253/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №19/26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2559,38 +2559,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>2804000</v>
+        <v>10844000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Tong Metall Servis AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>346612847</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000528839589001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №124/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №45/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,35 +2598,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>1048000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Оплата за товар по счет-фактуре №5400 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2634,40 +2639,40 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>3436000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>65893000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №96/26 от 03.08.2026</t>
+          <t>Оплата за сырье по договору №23/26 от 29.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2677,38 +2682,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>1062000</v>
+        <v>4522000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №87/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2445</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2718,38 +2723,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>2695000</v>
+        <v>3130000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №276/26 от 04.08.2026</t>
+          <t>Предоплата за товар по дог. №287/26 от 30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2757,40 +2762,35 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>1870000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Termiz Oziq-ovqat Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>259642823</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000044475498001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2426 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2799,34 +2799,39 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>12881000</v>
+        <v>5922000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Angren Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>308699114</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000400374503001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>IYUL OYI UCHUN ISH HAQI, REESTR №6468</t>
+          <t>Оплата за транспортные услуги по договору №229/26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2834,23 +2839,23 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>16262000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>26549000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Angren Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>309130513</t>
+          <t>364282370</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000231828708001</t>
+          <t>20208000447549855001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2860,14 +2865,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №248/26</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6711 03.08.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2877,38 +2882,38 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>864000</v>
+        <v>1051000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №116/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №5212 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2916,40 +2921,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>7033000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>1043000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №204/26</t>
+          <t>Оплата за продукцию по договору №223/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2959,21 +2964,21 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>17811000</v>
+        <v>4512000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2983,14 +2988,14 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №151/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №88/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3000,38 +3005,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>1529000</v>
+        <v>3646000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8136 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №242/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3040,39 +3045,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1484000</v>
+        <v>2243000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>344740732</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000981258976001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №29/22</t>
+          <t>Оплата за упаковочные материалы, с/ф №6588</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3081,39 +3086,34 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>7225000</v>
+        <v>12881000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Durdona Farm Savdo XK</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>318867866</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000278876047001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4070</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3123,38 +3123,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>49322000</v>
+        <v>2361000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №158/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №9012 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3164,38 +3164,38 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>32207000</v>
+        <v>843000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Shartnoma №96/26 bo'yicha oldindan to'lov</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №166/26 ОТ 07.08.2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3204,32 +3204,32 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>16732000</v>
+        <v>2343000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Guliston Tekstil MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>392648014</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000213542681001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №169/26 от 10.08.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №250/26</t>
         </is>
       </c>
     </row>
@@ -3244,40 +3244,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>26555000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>4918000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №78/26</t>
+          <t>Оплата за продукцию по дог. №50/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3287,38 +3287,38 @@
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>1821000</v>
+        <v>1909000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7286 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №3937 10.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3326,40 +3326,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>1486000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>1484000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Xiva Qurilish MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>372008215</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000784862057001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №43/26 от 17.08.2026</t>
+          <t>Аренда помещения за август, дог. №48/22</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3369,38 +3369,38 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>1482000</v>
+        <v>967000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Angren Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>364282370</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000447549855001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №69/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №44/26 от 11.08.2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3408,40 +3408,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>921000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>2412000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Farg'ona Qurilish AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №81/26 от 17.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №7272</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3449,40 +3449,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>1757000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>4365000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Non XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>247081109</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000749168910001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №160/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,40 +3490,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>1757000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>1247000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Предоплата за товар по дог. №241/26 от 12.08.2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3533,38 +3533,38 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>7460000</v>
+        <v>12276000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №58 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №380 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3574,38 +3574,38 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>1104000</v>
+        <v>7474000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №112/26 от 18.08.2026</t>
+          <t>Оплата по с/ф №3294 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3615,38 +3615,38 @@
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>952000</v>
+        <v>2353000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №259/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №220/26 от 14.08.2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3654,40 +3654,40 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>12761000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>1757000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №299/26, НДС 12%</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3695,40 +3695,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>2221000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>1757000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3713 за поставленный товар</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,40 +3736,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>1046000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>7173000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №823</t>
+          <t>Оплата за сырье по договору №37/26 от 14.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3779,38 +3779,38 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>6772000</v>
+        <v>3169000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №170/26, НДС 12%</t>
+          <t>Shartnoma №231/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3818,35 +3818,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>12100000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>2750000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9037)</t>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>16307000271935222417</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9037 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата по счет-фактуре №7193 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3854,40 +3859,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>2408000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>2050000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Оплата за продукцию по договору №106/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3897,38 +3902,38 @@
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>10380000</v>
+        <v>1626000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Qarshi Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>397457622</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000801727020001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4095 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №249/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3938,21 +3943,21 @@
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>9049000</v>
+        <v>868000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Tong Non XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>247081109</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000749168910001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3962,14 +3967,14 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1843</t>
+          <t>Оплата за продукцию по договору №152/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3979,21 +3984,21 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>4393000</v>
+        <v>1138000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4003,14 +4008,14 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3284 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №90/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4018,40 +4023,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>3977000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>6710000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №4931 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за транспортные услуги по договору №116/26</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4061,38 +4066,38 @@
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>2979000</v>
+        <v>3512000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5193</t>
+          <t>Предоплата за товар по договору №96/26 от 19.08.2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4100,23 +4105,23 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>50988000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>1559000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Durdona Farm Savdo XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>318867866</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000278876047001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4126,14 +4131,14 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2397</t>
+          <t>Предоплата за товар по договору №134/26 от 19.08.2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4143,38 +4148,38 @@
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>1235000</v>
+        <v>1002000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №243/26 от 25.08.2026</t>
+          <t>Оплата по чет-фактуре №948 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4184,38 +4189,38 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>2463000</v>
+        <v>958000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №70/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №55/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4228,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>1663000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>2267000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Angren Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>308699114</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000400374503001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №162/26 от 26.08.2026</t>
+          <t>Оплата за транспортные услуги по договору №244/26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4265,39 +4270,39 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>31091000</v>
+        <v>2645000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>309130513</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000231828708001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1463</t>
+          <t>Оплата за транспортные услуги по договору №169/26</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4306,39 +4311,39 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>928000</v>
+        <v>6113000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Metall MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>326261219</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000336102030001</t>
+          <t>20208000047610261001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товары согласно с/ф №489</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4346,40 +4351,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>1836000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>7971000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lazzat Meva Eksport MChJ</t>
+          <t>Sharq Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>271470811</t>
+          <t>330442725</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000907491689001</t>
+          <t>20208000455854785001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №30/26 от 28.08.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №3362</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4389,38 +4394,38 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>1667000</v>
+        <v>2598000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Tong Metall Servis AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>346612847</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000528839589001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №5655 28.08.2026, QQS BILAN</t>
+          <t>Предоплата за товар по договору №232/26 от 20.08.2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4429,39 +4434,34 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>4908000</v>
+        <v>12100000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>297466128</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9037)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>16307000271935222417</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №10/26</t>
+          <t>Kredit shartnomasi L-2024-9037 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,40 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>9521000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>2486000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №172/26 от 31.08.2026</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4512,38 +4512,38 @@
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>1602000</v>
+        <v>48168000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №105/26 от 31.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3080 24.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4553,38 +4553,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>1063000</v>
+        <v>3203000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7853 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №4247 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4592,35 +4592,40 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>2731000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за продукцию по договору №129/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4629,39 +4634,39 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>10651000</v>
+        <v>928000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000185907515001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №68/26 от 31.08.2026, НДС 12%</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4669,40 +4674,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>3192000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>5756000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Farg'ona Qurilish AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №280/26 от 02.09.2026</t>
+          <t>Оплата за сырье по договору №96/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4710,40 +4715,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>2095000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>12061000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №99/26 от 02.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №7889</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4753,38 +4758,38 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>3998000</v>
+        <v>1668000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №59/26 от 03.09.2026</t>
+          <t>Предоплата за товар по дог. №45/26 от 25.08.2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4792,40 +4797,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>15963000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>3759000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lazzat Meva Eksport MChJ</t>
+          <t>Angren Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>271470811</t>
+          <t>308699114</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000907491689001</t>
+          <t>20208000400374503001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3344 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1067</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4833,40 +4838,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>6722000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>4589000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Sharq Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>330442725</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000455854785001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3398 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №274/26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4876,38 +4881,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>5822000</v>
+        <v>6404000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №102/26 от 07.09.2026</t>
+          <t>Предоплата за товар по договору №75/26 от 26.08.2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4917,38 +4922,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>2686000</v>
+        <v>1476000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №117/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №7806 26.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4958,38 +4963,38 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>1907000</v>
+        <v>2395000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Termiz Oziq-ovqat Savdo AJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>259642823</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000044475498001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2062 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №8344 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4997,40 +5002,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>1474000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>2323000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №222/26 от 07.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №1683</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5038,23 +5043,23 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>1294000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>12896000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5064,14 +5069,14 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3475 07.09.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №217/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5081,38 +5086,38 @@
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>1263000</v>
+        <v>19492000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9028 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5061 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5120,40 +5125,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>1494000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>13421000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>344740732</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000981258976001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>АРЕНДНАЯ ПЛАТА ЗА СЕНТЯБРЬ 2026 Г. ПО ДОГОВОРУ №29/22</t>
+          <t>Предоплата за товар по договору №75/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5161,23 +5166,23 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>5373000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>11484000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Durdona Farm Savdo XK</t>
+          <t>Tong Non XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>318867866</t>
+          <t>247081109</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000278876047001</t>
+          <t>20208000749168910001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5187,14 +5192,14 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8038</t>
+          <t>Оплата за товар по счет-фактуре №7271 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5203,39 +5208,34 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>6132000</v>
+        <v>300000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>297466128</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №284/26</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5244,34 +5244,39 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>12967000</v>
+        <v>3423000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Farg'ona Qurilish AJ</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Tovarlar uchun to'lov h/f №3413</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5280,39 +5285,39 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>19256000</v>
+        <v>4047000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Durdona Farm Savdo XK</t>
+          <t>Namangan Metall MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>318867866</t>
+          <t>326261219</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000278876047001</t>
+          <t>20208000047610261001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №221/26 от 07.09.2026, НДС 12%</t>
+          <t>Оплата за сырье по договору №252/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5320,40 +5325,40 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>43474000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>5728000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №88/26 от 08.09.2026</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №259/26 ОТ 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5361,40 +5366,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>4443000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>77973000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6107 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №180/26</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5404,21 +5409,21 @@
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>3407000</v>
+        <v>7790000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5428,14 +5433,14 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №1124 ОТ 09.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №759 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5444,39 +5449,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>5185000</v>
+        <v>4766000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9333</t>
+          <t>Оплата за упаковочные материалы, с/ф №5245</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5486,38 +5491,38 @@
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>7607000</v>
+        <v>2191000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Termiz Oziq-ovqat Savdo AJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>259642823</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000044475498001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №32/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №285/26 от 02.09.2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5527,38 +5532,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>3350000</v>
+        <v>1973000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №165/26 от 10.09.2026</t>
+          <t>Оплата за товар по с/ф №364 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5566,40 +5571,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>7664000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>1968000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №196/26 от 10.09.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №127/26 от 02.09.2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5607,40 +5612,40 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>2374000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>10322000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Sut Mahsulotlari XK</t>
+          <t>Sharq Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>335974576</t>
+          <t>230815755</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000268017270001</t>
+          <t>20208000109215286001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7200</t>
+          <t>Оплата за сырье по договору №235/26 от 02.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5650,38 +5655,38 @@
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>1195000</v>
+        <v>1566000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Tong Non XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>247081109</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000749168910001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №197/26 от 11.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9288</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5691,38 +5696,38 @@
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>3208000</v>
+        <v>1080000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Termiz Oziq-ovqat Savdo AJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>259642823</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000044475498001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №247/26 от 14.09.2026</t>
+          <t>Shartnoma №179/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5732,38 +5737,38 @@
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>8921000</v>
+        <v>17580000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №69/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №6/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5773,38 +5778,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>4354000</v>
+        <v>8430000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5835 от 15.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №2124 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5814,21 +5819,21 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>1344000</v>
+        <v>1319000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lazzat Meva Eksport MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>271470811</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000907491689001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5838,14 +5843,14 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №64/26 от 15.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3820</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5854,39 +5859,34 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>5603000</v>
+        <v>12967000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>297466128</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №219/26 ОТ 15.09.2026, НДС 12%</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №3970</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5894,40 +5894,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>2034000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>1494000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Termiz Oziq-ovqat Savdo AJ</t>
+          <t>Xiva Qurilish MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>259642823</t>
+          <t>372008215</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000044475498001</t>
+          <t>20208000784862057001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5921 от 16.09.2026, в т.ч. НДС 12%</t>
+          <t>Аренда помещения за сентябрь, дог. №48/22</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5935,40 +5935,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>1972000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>13366000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №199/26 от 16.09.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №56/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5978,38 +5978,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>1312000</v>
+        <v>945000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9267 от 16.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №94/26 от 09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6018,39 +6018,39 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>1768000</v>
+        <v>5202000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Оплата за сырье по договору №24/26 от 09.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6058,40 +6058,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>1768000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>20793000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Предоплата за товар по дог. №273/26 от 10.09.2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6101,21 +6101,21 @@
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>10599000</v>
+        <v>1163000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Tong Non XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>247081109</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000749168910001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6125,14 +6125,14 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №85/26 от 17.09.2026</t>
+          <t>Предоплата за товар по дог. №15/26 от 10.09.2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6140,40 +6140,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>1306000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>16497000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4486 от 18.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №43/26</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6181,35 +6181,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>12100000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>1050000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9037)</t>
+          <t>Andijon Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>16307000271935222417</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9037 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по счет-фактуре №4342 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6219,38 +6224,38 @@
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>25349000</v>
+        <v>889000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Termiz Oziq-ovqat Savdo AJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>259642823</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000044475498001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №108/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №110 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6258,40 +6263,40 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>2647000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>3849000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Farg'ona Qurilish AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №236/26 от 21.09.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №5381</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6300,39 +6305,39 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>5109000</v>
+        <v>9061000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Denov Moy MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>309130513</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000231828708001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы,с/ф №6250</t>
+          <t>Оплата за упаковочные материалы, с/ф №5467</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6341,39 +6346,39 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>7405000</v>
+        <v>1768000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Guliston Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>392648014</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000213542681001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №11/26</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6382,39 +6387,39 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>15495000</v>
+        <v>1768000</v>
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6746</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6422,40 +6427,40 @@
           <t>244</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>7188000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>4072000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №747 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №50/26</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6463,23 +6468,23 @@
           <t>245</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>2256000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>62681000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Farg'ona Qurilish AJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>349841444</t>
+          <t>318345235</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000500078240001</t>
+          <t>20208000564439630001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6489,14 +6494,14 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №272/26 от 22.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №3563</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6504,40 +6509,40 @@
           <t>246</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>24785000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>14848000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Farovon Sut MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>297466128</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000735288395001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №238/26</t>
+          <t>Оплата за товар по счет-фактуре №1463 от 17.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6545,40 +6550,40 @@
           <t>247</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>43841000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>3229000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Durdona Farm Savdo XK</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>318867866</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000278876047001</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №4/26</t>
+          <t>Оплата за товар по счет-фактуре №8381 от 17.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6588,38 +6593,38 @@
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>3740000</v>
+        <v>1025000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Urganch Polimer MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>386786602</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000887604707001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №280/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №1907 от 17.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6627,40 +6632,40 @@
           <t>249</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>2459000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>1007000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Yog'och AJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
+          <t>Оплата за продукцию по договору №88/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6668,40 +6673,40 @@
           <t>250</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>2538000</v>
-      </c>
+      <c r="C160" s="2" t="n">
+        <v>6613000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №51/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №213/26</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6710,39 +6715,39 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>934000</v>
+        <v>12875000</v>
       </c>
       <c r="D161" s="2" t="n"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000336102030001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>Оплата за упаковочные материалы, с/ф №842</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6750,40 +6755,35 @@
           <t>252</t>
         </is>
       </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>2773000</v>
-      </c>
+      <c r="C162" s="2" t="n">
+        <v>12100000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>245987287</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9037)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>16307000271935222417</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8519 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2024-9037 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6793,21 +6793,21 @@
       </c>
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="n">
-        <v>2558000</v>
+        <v>4473000</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Lazzat Meva Eksport MChJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>271470811</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000907491689001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №32/26 от 25.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №251</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6834,38 +6834,38 @@
       </c>
       <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="n">
-        <v>1832000</v>
+        <v>1839000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Angren Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>364282370</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000447549855001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №128/26 от 28.09.2026</t>
+          <t>Оплата за продукцию по дог. №290/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6875,38 +6875,38 @@
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="n">
-        <v>1702000</v>
+        <v>1679000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Durdona Qurilish XK</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>245987287</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000016416659001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9722</t>
+          <t>Предоплата за товар по договору №16/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6916,21 +6916,21 @@
       </c>
       <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="n">
-        <v>1095000</v>
+        <v>1438000</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lazzat Meva Eksport MChJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>271470811</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000907491689001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6940,14 +6940,14 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7979 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1099 21.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6956,39 +6956,39 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>15590000</v>
+        <v>2462000</v>
       </c>
       <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Durdona Farm Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>318867866</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000278876047001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №160/26</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6996,40 +6996,40 @@
           <t>258</t>
         </is>
       </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n">
-        <v>2706000</v>
-      </c>
+      <c r="C168" s="2" t="n">
+        <v>4172000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Termiz Oziq-ovqat Savdo AJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>259642823</t>
+          <t>340732898</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000044475498001</t>
+          <t>20208000258976133001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №101/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №5275</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7039,38 +7039,38 @@
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>1250000</v>
+        <v>23580000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Termiz Oziq-ovqat Savdo AJ</t>
+          <t>Andijon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>259642823</t>
+          <t>384144405</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000044475498001</t>
+          <t>20208000007824026001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №36/26 ОТ 29.09.2026</t>
+          <t>Shartnoma №107/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7078,35 +7078,40 @@
           <t>260</t>
         </is>
       </c>
-      <c r="C170" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>5331000</v>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Kamalak Yog'och AJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>264801452</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000354268182001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №238/26 ОТ 22.09.2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7114,59 +7119,874 @@
           <t>261</t>
         </is>
       </c>
-      <c r="C171" s="2" t="n">
-        <v>10044000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>14820000</v>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Guliston Tekstil MChJ</t>
+          <t>Navoiy Mebel MChJ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>392648014</t>
+          <t>398728780</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20208000213542681001</t>
+          <t>20208000641665900001</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №121/26 от 30.09.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №7312 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v>616247000</v>
-      </c>
-      <c r="D172" s="4" t="n">
-        <v>618747000</v>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>1139000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Kamalak Yog'och AJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>264801452</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000354268182001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №206/26 от 23.09.2026</t>
+        </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>1072000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №4007 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>943000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Andijon Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>384144405</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000007824026001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №221/26 ОТ 23.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>934000</v>
+      </c>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000185907515001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>4883000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Angren Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>308699114</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000400374503001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №204/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n">
+        <v>5301000</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Andijon Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>384144405</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000007824026001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №5296 от 25.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>6284000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Sharq Dori-Darmon AJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>330442725</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000455854785001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №102/26 от 25.09.2026, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>7825000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Sharq Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>230815755</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20208000109215286001</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №9068</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n">
+        <v>7142000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Kamalak Yog'och AJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>264801452</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000354268182001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №2038 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n">
+        <v>4611000</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Tong Non XK</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>247081109</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000749168910001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №7061 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n">
+        <v>3660000</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №9780 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n">
+        <v>1991000</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №171/26 от 28.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n">
+        <v>1604000</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Andijon Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>384144405</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>20208000007824026001</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №242/26 от 28.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n">
+        <v>1178000</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №281/26 от 28.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n">
+        <v>1058000</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n">
+        <v>2178000</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №8612 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Shartnoma №5/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n">
+        <v>1331000</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №192/26 от 29.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="2" t="n">
+        <v>28530000</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Navoiy Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>398728780</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>20208000641665900001</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №280/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Bodomzor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>КОМИССИЯ БАНКА ЗА РАСЧЕТНО-КАССОВОЕ ОБСЛУЖИВАНИЕ ЗА СЕНТЯБРЬ</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>619246000</v>
+      </c>
+      <c r="D192" s="4" t="n">
+        <v>621746000</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C173" s="4" t="n">
+      <c r="C193" s="4" t="n">
         <v>68200000</v>
       </c>
-      <c r="D173" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
